--- a/public/assets/documents/excel/sample_upload/Company.xlsx
+++ b/public/assets/documents/excel/sample_upload/Company.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\xampp8.2\htdocs\NeoEHS_Karam1\public\assets\documents\excel\sample_upload\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\xampp8.2\htdocs\NeoEHS\NeoEHS_Karam\public\assets\documents\excel\sample_upload\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
     <t>SNo</t>
   </si>
@@ -31,24 +31,6 @@
   </si>
   <si>
     <t>Address</t>
-  </si>
-  <si>
-    <t>Type One Company</t>
-  </si>
-  <si>
-    <t>Tone</t>
-  </si>
-  <si>
-    <t>Type Two Company</t>
-  </si>
-  <si>
-    <t>Ttwo</t>
-  </si>
-  <si>
-    <t>Comapany2</t>
-  </si>
-  <si>
-    <t>Company1</t>
   </si>
 </sst>
 </file>
@@ -365,7 +347,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D1"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="3" width="17.109375" customWidth="1"/>
@@ -385,34 +367,6 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D3" t="s">
-        <v>8</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
